--- a/data/cva/processed/cva_applications.xlsx
+++ b/data/cva/processed/cva_applications.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/cva_analysis/data/cva/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE5FF10-D27F-3E46-A1BC-045A901FEEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A4F0EE-AB55-5A4F-98E1-BAA0D7F4D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{DEB9D464-1753-1546-B2D7-3FBA4605F8C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$39</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>study</t>
   </si>
@@ -332,15 +335,9 @@
     <t>Contribute to ecosystem-based fishery management</t>
   </si>
   <si>
-    <t>Identify research and data needs</t>
-  </si>
-  <si>
     <t>Inform management documents</t>
   </si>
   <si>
-    <t>Prioritize science needs and management interventions</t>
-  </si>
-  <si>
     <t>Prioritize research and data needs</t>
   </si>
   <si>
@@ -383,9 +380,6 @@
     <t>Assess vulnerability of fishing communities</t>
   </si>
   <si>
-    <t>Priorize species, Guide management actions</t>
-  </si>
-  <si>
     <t>Inform strategic planning</t>
   </si>
   <si>
@@ -399,6 +393,12 @@
   </si>
   <si>
     <t>Contribute to ecosystem-based fishery management, Identify environmental variables to include in stock assessment</t>
+  </si>
+  <si>
+    <t>Prioritize species, Guide management actions</t>
+  </si>
+  <si>
+    <t>Prioritize research and data needs, Identify management interventions</t>
   </si>
 </sst>
 </file>
@@ -837,36 +837,36 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -888,257 +888,257 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>60</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1149,64 +1149,64 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1220,44 +1220,44 @@
         <v>70</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1268,7 +1268,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -1279,172 +1279,172 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1455,13 +1455,13 @@
         <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1472,19 +1472,24 @@
         <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E39" xr:uid="{572E3B17-FEFF-8C4B-80E1-6A0FB18244A7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E39">
+      <sortCondition ref="C1:C39"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E36" r:id="rId1" display="https://www.mafmc.org/s/EAFM-Doc-Revised-2019-02-08.pdf" xr:uid="{12158CBF-94A0-6D43-93B8-C98515FB8548}"/>
+    <hyperlink ref="E26" r:id="rId1" display="https://www.mafmc.org/s/EAFM-Doc-Revised-2019-02-08.pdf" xr:uid="{12158CBF-94A0-6D43-93B8-C98515FB8548}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
